--- a/templates/PRAP_SourceData_Dummy_10x10_v1.10.xlsx
+++ b/templates/PRAP_SourceData_Dummy_10x10_v1.10.xlsx
@@ -1484,7 +1484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1540,8 +1540,7 @@
       <c r="D2" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="E2" s="9" t="n"/>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>Manager's own estimate - the assumptions understate this study</t>
         </is>
@@ -1567,7 +1566,6 @@
         <v>1.23</v>
       </c>
       <c r="E3" s="9" t="n"/>
-      <c r="F3" s="9" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -1589,7 +1587,6 @@
         <v>1.28</v>
       </c>
       <c r="E4" s="9" t="n"/>
-      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
@@ -1611,7 +1608,6 @@
         <v>1.34</v>
       </c>
       <c r="E5" s="9" t="n"/>
-      <c r="F5" s="9" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -1633,7 +1629,6 @@
         <v>1.4</v>
       </c>
       <c r="E6" s="9" t="n"/>
-      <c r="F6" s="9" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -1655,7 +1650,6 @@
         <v>1.48</v>
       </c>
       <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -1677,7 +1671,6 @@
         <v>1.56</v>
       </c>
       <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -1699,7 +1692,6 @@
         <v>1.65</v>
       </c>
       <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -1721,7 +1713,6 @@
         <v>1.74</v>
       </c>
       <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -1743,7 +1734,6 @@
         <v>1.84</v>
       </c>
       <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
@@ -1765,7 +1755,6 @@
         <v>1.94</v>
       </c>
       <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -1787,7 +1776,6 @@
         <v>2.04</v>
       </c>
       <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -1809,7 +1797,6 @@
         <v>2.15</v>
       </c>
       <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -1831,7 +1818,6 @@
         <v>2.26</v>
       </c>
       <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -1853,7 +1839,6 @@
         <v>2.38</v>
       </c>
       <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -1875,7 +1860,6 @@
         <v>2.5</v>
       </c>
       <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -1897,7 +1881,6 @@
         <v>2.62</v>
       </c>
       <c r="E18" s="9" t="n"/>
-      <c r="F18" s="9" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -1919,7 +1902,6 @@
         <v>2.75</v>
       </c>
       <c r="E19" s="9" t="n"/>
-      <c r="F19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
@@ -1941,7 +1923,6 @@
         <v>2.88</v>
       </c>
       <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -1963,7 +1944,6 @@
         <v>3.01</v>
       </c>
       <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
@@ -1985,7 +1965,6 @@
         <v>3.14</v>
       </c>
       <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -2007,7 +1986,6 @@
         <v>3.28</v>
       </c>
       <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -2029,7 +2007,6 @@
         <v>3.42</v>
       </c>
       <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -2051,7 +2028,6 @@
         <v>3.44</v>
       </c>
       <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -2073,7 +2049,6 @@
         <v>3.3</v>
       </c>
       <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -2095,7 +2070,6 @@
         <v>3.16</v>
       </c>
       <c r="E27" s="9" t="n"/>
-      <c r="F27" s="9" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -2117,7 +2091,6 @@
         <v>3.02</v>
       </c>
       <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -2139,7 +2112,6 @@
         <v>2.89</v>
       </c>
       <c r="E29" s="9" t="n"/>
-      <c r="F29" s="9" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -2161,7 +2133,6 @@
         <v>2.76</v>
       </c>
       <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -2183,7 +2154,6 @@
         <v>2.64</v>
       </c>
       <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -2205,7 +2175,6 @@
         <v>2.51</v>
       </c>
       <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -2227,7 +2196,6 @@
         <v>2.39</v>
       </c>
       <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -2249,7 +2217,6 @@
         <v>2.28</v>
       </c>
       <c r="E34" s="9" t="n"/>
-      <c r="F34" s="9" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -2271,7 +2238,6 @@
         <v>2.16</v>
       </c>
       <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -2293,7 +2259,6 @@
         <v>2.05</v>
       </c>
       <c r="E36" s="9" t="n"/>
-      <c r="F36" s="9" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -2315,7 +2280,6 @@
         <v>1.95</v>
       </c>
       <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -2337,7 +2301,6 @@
         <v>1.85</v>
       </c>
       <c r="E38" s="9" t="n"/>
-      <c r="F38" s="9" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -2359,7 +2322,6 @@
         <v>1.75</v>
       </c>
       <c r="E39" s="9" t="n"/>
-      <c r="F39" s="9" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -2381,7 +2343,6 @@
         <v>1.66</v>
       </c>
       <c r="E40" s="9" t="n"/>
-      <c r="F40" s="9" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -2403,7 +2364,6 @@
         <v>1.57</v>
       </c>
       <c r="E41" s="9" t="n"/>
-      <c r="F41" s="9" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -2425,7 +2385,6 @@
         <v>1.49</v>
       </c>
       <c r="E42" s="9" t="n"/>
-      <c r="F42" s="9" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -2447,7 +2406,6 @@
         <v>1.41</v>
       </c>
       <c r="E43" s="9" t="n"/>
-      <c r="F43" s="9" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -2468,8 +2426,7 @@
       <c r="D44" s="9" t="n">
         <v>0.35</v>
       </c>
-      <c r="E44" s="9" t="n"/>
-      <c r="F44" s="9" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>Agreed with the study lead</t>
         </is>
@@ -2495,7 +2452,6 @@
         <v>0.4</v>
       </c>
       <c r="E45" s="9" t="n"/>
-      <c r="F45" s="9" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -2517,7 +2473,6 @@
         <v>0.45</v>
       </c>
       <c r="E46" s="9" t="n"/>
-      <c r="F46" s="9" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -2539,7 +2494,6 @@
         <v>0.5</v>
       </c>
       <c r="E47" s="9" t="n"/>
-      <c r="F47" s="9" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -2561,7 +2515,6 @@
         <v>0.35</v>
       </c>
       <c r="E48" s="9" t="n"/>
-      <c r="F48" s="9" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -2583,7 +2536,6 @@
         <v>0.4</v>
       </c>
       <c r="E49" s="9" t="n"/>
-      <c r="F49" s="9" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -2605,7 +2557,6 @@
         <v>0.45</v>
       </c>
       <c r="E50" s="9" t="n"/>
-      <c r="F50" s="9" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -2627,7 +2578,6 @@
         <v>0.5</v>
       </c>
       <c r="E51" s="9" t="n"/>
-      <c r="F51" s="9" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -2649,7 +2599,6 @@
         <v>0.35</v>
       </c>
       <c r="E52" s="9" t="n"/>
-      <c r="F52" s="9" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -2671,7 +2620,6 @@
         <v>0.4</v>
       </c>
       <c r="E53" s="9" t="n"/>
-      <c r="F53" s="9" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
@@ -2693,7 +2641,6 @@
         <v>0.45</v>
       </c>
       <c r="E54" s="9" t="n"/>
-      <c r="F54" s="9" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -2715,7 +2662,6 @@
         <v>0.5</v>
       </c>
       <c r="E55" s="9" t="n"/>
-      <c r="F55" s="9" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -2737,7 +2683,6 @@
         <v>0.35</v>
       </c>
       <c r="E56" s="9" t="n"/>
-      <c r="F56" s="9" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
@@ -2759,7 +2704,6 @@
         <v>0.4</v>
       </c>
       <c r="E57" s="9" t="n"/>
-      <c r="F57" s="9" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
@@ -2781,7 +2725,6 @@
         <v>0.45</v>
       </c>
       <c r="E58" s="9" t="n"/>
-      <c r="F58" s="9" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
@@ -2803,7 +2746,6 @@
         <v>0.5</v>
       </c>
       <c r="E59" s="9" t="n"/>
-      <c r="F59" s="9" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
@@ -2825,7 +2767,6 @@
         <v>0.35</v>
       </c>
       <c r="E60" s="9" t="n"/>
-      <c r="F60" s="9" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
@@ -2847,7 +2788,6 @@
         <v>0.4</v>
       </c>
       <c r="E61" s="9" t="n"/>
-      <c r="F61" s="9" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
@@ -2869,7 +2809,6 @@
         <v>0.45</v>
       </c>
       <c r="E62" s="9" t="n"/>
-      <c r="F62" s="9" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
@@ -2891,7 +2830,6 @@
         <v>0.5</v>
       </c>
       <c r="E63" s="9" t="n"/>
-      <c r="F63" s="9" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
@@ -2913,7 +2851,6 @@
         <v>0.35</v>
       </c>
       <c r="E64" s="9" t="n"/>
-      <c r="F64" s="9" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
@@ -2935,7 +2872,6 @@
         <v>0.4</v>
       </c>
       <c r="E65" s="9" t="n"/>
-      <c r="F65" s="9" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
@@ -2957,7 +2893,6 @@
         <v>0.45</v>
       </c>
       <c r="E66" s="9" t="n"/>
-      <c r="F66" s="9" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
@@ -2979,7 +2914,6 @@
         <v>0.5</v>
       </c>
       <c r="E67" s="9" t="n"/>
-      <c r="F67" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
